--- a/assets/template/A09_04_Stability_Study_Samples.xlsx
+++ b/assets/template/A09_04_Stability_Study_Samples.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\qc\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A40020-C4E9-4048-B850-E9DFF8E8E8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32791DF3-B13E-49E8-BF9D-2EFCB05CC279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -169,6 +169,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -189,9 +192,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -574,34 +574,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10"/>
-      <c r="B1" s="10"/>
-      <c r="C1" s="13" t="s">
+      <c r="A1" s="11"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
     </row>
     <row r="2" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="7" t="s">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="9" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
@@ -640,7 +640,7 @@
     </row>
     <row r="5" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
-      <c r="B5" s="14"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -652,7 +652,7 @@
     </row>
     <row r="6" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
-      <c r="B6" s="14"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -664,7 +664,7 @@
     </row>
     <row r="7" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
-      <c r="B7" s="14"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -676,7 +676,7 @@
     </row>
     <row r="8" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
-      <c r="B8" s="14"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
@@ -688,7 +688,7 @@
     </row>
     <row r="9" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
-      <c r="B9" s="14"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -700,7 +700,7 @@
     </row>
     <row r="10" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="14"/>
+      <c r="B10" s="6"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
@@ -712,7 +712,7 @@
     </row>
     <row r="11" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
-      <c r="B11" s="14"/>
+      <c r="B11" s="6"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -724,7 +724,7 @@
     </row>
     <row r="12" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
-      <c r="B12" s="14"/>
+      <c r="B12" s="6"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -736,7 +736,7 @@
     </row>
     <row r="13" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="B13" s="14"/>
+      <c r="B13" s="6"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -748,7 +748,7 @@
     </row>
     <row r="14" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
-      <c r="B14" s="14"/>
+      <c r="B14" s="6"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
@@ -760,7 +760,7 @@
     </row>
     <row r="15" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
-      <c r="B15" s="14"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -772,7 +772,7 @@
     </row>
     <row r="16" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
-      <c r="B16" s="14"/>
+      <c r="B16" s="6"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -784,7 +784,7 @@
     </row>
     <row r="17" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="14"/>
+      <c r="B17" s="6"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -796,7 +796,7 @@
     </row>
     <row r="18" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
-      <c r="B18" s="14"/>
+      <c r="B18" s="6"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
@@ -807,92 +807,92 @@
       <c r="J18" s="5"/>
     </row>
     <row r="20" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="11" t="s">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -911,8 +911,8 @@
   <pageSetup scale="74" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;"Times New Roman,Regular"Mã số phụ lục / Appendix No.
-0000034_A01_03&amp;C&amp;"Times New Roman,Regular"Ngày hiệu lực / Appendix
-effective 01/01/2026&amp;R&amp;"Times New Roman,Regular"Trang / Page
+0000034_A01_04&amp;C&amp;"Times New Roman,Regular"Ngày hiệu lực / Appendix
+effective 10/04/2026&amp;R&amp;"Times New Roman,Regular"Trang / Page
 &amp;P/&amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId2"/>

--- a/assets/template/A09_04_Stability_Study_Samples.xlsx
+++ b/assets/template/A09_04_Stability_Study_Samples.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\qc\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32791DF3-B13E-49E8-BF9D-2EFCB05CC279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FD385E-5983-4A8A-8998-F6ADDACCEBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,27 +66,27 @@
 No.</t>
   </si>
   <si>
-    <t>Người theo dõi / Monitored by
-Ngày / Date:</t>
-  </si>
-  <si>
-    <t>Người kiểm tra / Reviewed by
-Ngày / Date:</t>
-  </si>
-  <si>
     <t>Mã số phòng / tủ 
 Room No. / Equip. No.</t>
   </si>
   <si>
     <t>Điều kiện
 Condition</t>
+  </si>
+  <si>
+    <t>Người theo dõi / Ngày
+Monitored by / Date</t>
+  </si>
+  <si>
+    <t>Người xem xét / Ngày
+Reviewed by / Date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,8 +116,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="2">
@@ -128,7 +134,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -151,6 +157,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -175,23 +196,23 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -565,7 +586,8 @@
     <col min="2" max="2" width="34.42578125" style="2" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="14" style="2" customWidth="1"/>
-    <col min="5" max="6" width="18" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.42578125" style="2" customWidth="1"/>
     <col min="8" max="8" width="12" style="2" customWidth="1"/>
     <col min="9" max="9" width="12.7109375" style="2" customWidth="1"/>
@@ -574,9 +596,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11"/>
-      <c r="B1" s="11"/>
-      <c r="C1" s="14" t="s">
+      <c r="A1" s="9"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="10" t="s">
         <v>9</v>
       </c>
       <c r="D1" s="7"/>
@@ -588,20 +610,20 @@
       <c r="J1" s="7"/>
     </row>
     <row r="2" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="14"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
@@ -807,20 +829,20 @@
       <c r="J18" s="5"/>
     </row>
     <row r="20" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
+      <c r="A20" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
